--- a/data/GreatLink/GreatLink Multi-Sector Income_Dividends.xlsx
+++ b/data/GreatLink/GreatLink Multi-Sector Income_Dividends.xlsx
@@ -7,7 +7,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="DividendHistory" sheetId="1" r:id="GemRid762730"/>
+    <sheet name="DividendHistory" sheetId="1" r:id="GemRid957750"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>XD Date</t>
   </si>
@@ -26,10 +26,13 @@
     <t>Gross Dividend</t>
   </si>
   <si>
+    <t>30/10/2025</t>
+  </si>
+  <si>
+    <t>0.005</t>
+  </si>
+  <si>
     <t>01/10/2025</t>
-  </si>
-  <si>
-    <t>0.005</t>
   </si>
   <si>
     <t>01/09/2025</t>
@@ -615,6 +618,17 @@
         <v>4</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" t="s">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="1.8" right="1.8" top="1.8999999999999999" bottom="1.8999999999999999" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" scale="100" paperSize="0" firstPageNumber="1" fitToWidth="0" fitToHeight="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
